--- a/sponsorship_form_templates/012_event_sponsorship_inquiry_form--sponsorship_form_templates.xlsx
+++ b/sponsorship_form_templates/012_event_sponsorship_inquiry_form--sponsorship_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -972,8 +972,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'event_organizer'}</t>
+          <t>event_organizer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Event Organizer'}</t>
+          <t>Event Organizer</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'event_coordinator'}</t>
+          <t>event_coordinator</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Event Coordinator'}</t>
+          <t>Event Coordinator</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'partnership'}</t>
+          <t>partnership</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Partnership'}</t>
+          <t>Partnership</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'collaborative_partnership'}</t>
+          <t>collaborative_partnership</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Collaborative Partnership'}</t>
+          <t>Collaborative Partnership</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
